--- a/data/availability/projects/al-marasem-developments/marbay-ras-el-hekma.xlsx
+++ b/data/availability/projects/al-marasem-developments/marbay-ras-el-hekma.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Handover 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Handover 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Handover 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Handover 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Handover 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -909,7 +909,6 @@
       <c r="G2" t="n">
         <v>98</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -920,7 +919,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Handover 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -966,7 +965,6 @@
       <c r="G3" t="n">
         <v>127</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -977,7 +975,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Handover 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1023,7 +1021,6 @@
       <c r="G4" t="n">
         <v>155</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -1034,7 +1031,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Handover 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1080,7 +1077,6 @@
       <c r="G5" t="n">
         <v>175</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -1091,7 +1087,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Handover 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1137,7 +1133,6 @@
       <c r="G6" t="n">
         <v>220</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -1148,7 +1143,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Handover 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
